--- a/documentation/Non-generated material/Information and Decision Flow.xlsx
+++ b/documentation/Non-generated material/Information and Decision Flow.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/documentation/Non-generated material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{1A78604C-994E-4887-A3EA-D1B833B5572B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C461E627-9986-48F5-BC47-EB495AD897B1}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="8_{1A78604C-994E-4887-A3EA-D1B833B5572B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{372188BD-D174-446B-BF35-0FD259C9FDFB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{058C4FC8-23DA-4D31-B0E5-29113FDE895B}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" activeTab="1" xr2:uid="{058C4FC8-23DA-4D31-B0E5-29113FDE895B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1 (3)" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="29">
   <si>
     <t>Time</t>
   </si>
@@ -105,14 +106,32 @@
     <t>D+</t>
   </si>
   <si>
-    <t>1. Creating Day-Ahead bids and fixing plant flows (D-1 11:55)</t>
+    <t>Creating Day-Ahead bids and fixing plant flows (D-1 11:55)</t>
+  </si>
+  <si>
+    <t>Decision horizon</t>
+  </si>
+  <si>
+    <t>Plant flows + intraday</t>
+  </si>
+  <si>
+    <t>Plant flows</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Planning horizon</t>
+  </si>
+  <si>
+    <t>SS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,8 +153,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,8 +193,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -416,13 +467,234 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDot">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDot">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDot">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,10 +802,140 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,6 +953,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1149,23 +1555,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68894A8-7C63-4694-A590-173BDA6A7464}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
     <col min="2" max="2" width="4.140625" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
     <col min="4" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="38" t="s">
+        <v>27</v>
+      </c>
       <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1176,7 +1587,7 @@
       <c r="C2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="39" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="18" t="s">
@@ -1196,7 +1607,7 @@
       <c r="C3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="40" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="21" t="s">
@@ -1230,16 +1641,14 @@
       <c r="C5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="56"/>
+      <c r="G5" s="44" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="16"/>
@@ -1250,18 +1659,12 @@
       <c r="C6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="58"/>
+      <c r="E6" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>15</v>
-      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="45"/>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1272,16 +1675,14 @@
       <c r="C7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="53" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="16"/>
@@ -1290,20 +1691,12 @@
       <c r="A8" s="16"/>
       <c r="B8" s="33"/>
       <c r="C8" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>16</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="54"/>
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1316,12 +1709,302 @@
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="12">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D7:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C6BF89-C17B-4270-B6EB-0F7C02D04422}">
+  <dimension ref="A1:P30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="37"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="56"/>
+      <c r="G5" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="65"/>
+      <c r="E6" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="50"/>
+      <c r="G7" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="63"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="77"/>
+      <c r="F13" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="80"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+    </row>
+    <row r="21" spans="7:16" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="7:16" x14ac:dyDescent="0.25">
+      <c r="P30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D10:F11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G5:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
